--- a/Result/profitability/3206.xlsx
+++ b/Result/profitability/3206.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.23</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4675</v>
+        <v>0.455</v>
       </c>
       <c r="N2" t="n">
-        <v>22.00375</v>
+        <v>21.8575</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4225</v>
+        <v>0.42125</v>
       </c>
       <c r="N3" t="n">
-        <v>22.42625</v>
+        <v>22.505</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.25</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3825</v>
+        <v>0.375</v>
       </c>
       <c r="N4" t="n">
-        <v>22.32</v>
+        <v>22.2775</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.26</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2725</v>
+        <v>0.28125</v>
       </c>
       <c r="N5" t="n">
-        <v>21.81</v>
+        <v>21.77625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.18</v>
       </c>
       <c r="M6" t="n">
-        <v>0.18875</v>
+        <v>0.21125</v>
       </c>
       <c r="N6" t="n">
-        <v>21.00375</v>
+        <v>21.19125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.09</v>
       </c>
       <c r="M7" t="n">
-        <v>0.13</v>
+        <v>0.13375</v>
       </c>
       <c r="N7" t="n">
-        <v>20.73625</v>
+        <v>20.6625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.53</v>
       </c>
       <c r="M8" t="n">
-        <v>0.13</v>
+        <v>0.1675</v>
       </c>
       <c r="N8" t="n">
-        <v>21.2425</v>
+        <v>21.265</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>876</v>
+      </c>
+      <c r="D75" t="n">
+        <v>694</v>
+      </c>
+      <c r="E75" t="n">
+        <v>182</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="G75" t="n">
+        <v>42</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.84%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>42</v>
+      </c>
+      <c r="K75" t="n">
+        <v>33</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.50875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>20.8375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.153846153846154</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.1799999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.008716707021791725</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.142857142857143</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.2700000000000031</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01279620853080587</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
